--- a/dataset/Faulty/buffer_underrun_dynamic.xlsx
+++ b/dataset/Faulty/buffer_underrun_dynamic.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -456,14 +456,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -478,14 +478,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -500,14 +500,14 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -522,14 +522,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -588,14 +588,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -610,14 +610,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -632,14 +632,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -654,14 +654,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -676,14 +676,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -698,14 +698,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -720,14 +720,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -742,14 +742,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -764,14 +764,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -786,14 +786,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -808,14 +808,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -830,14 +830,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -852,14 +852,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -874,14 +874,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -896,14 +896,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -918,14 +918,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -940,14 +940,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -962,14 +962,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -984,14 +984,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1006,14 +1006,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1028,14 +1028,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1050,14 +1050,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1072,14 +1072,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1094,14 +1094,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1116,14 +1116,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1138,14 +1138,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1160,14 +1160,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1182,14 +1182,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1204,14 +1204,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1226,14 +1226,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1248,14 +1248,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1270,14 +1270,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
+          <t>dataset/itc-benchmarks/01.w_Defects/buffer_underrun_dynamic.c</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Faulty</t>
+          <t>faulty</t>
         </is>
       </c>
     </row>
